--- a/artfynd/A 20212-2024 artfynd.xlsx
+++ b/artfynd/A 20212-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126276218</v>
       </c>
       <c r="B2" t="n">
-        <v>58367</v>
+        <v>58371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>126276199</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
+        <v>57068</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>126276209</v>
       </c>
       <c r="B4" t="n">
-        <v>58080</v>
+        <v>58084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20212-2024 artfynd.xlsx
+++ b/artfynd/A 20212-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126276218</v>
       </c>
       <c r="B2" t="n">
-        <v>58371</v>
+        <v>58374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>126276199</v>
       </c>
       <c r="B3" t="n">
-        <v>57068</v>
+        <v>57069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>126276209</v>
       </c>
       <c r="B4" t="n">
-        <v>58084</v>
+        <v>58087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
